--- a/import-templates/project-import-template.xlsx
+++ b/import-templates/project-import-template.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Template" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Dropdown Values" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Instructions" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="83">
   <si>
     <t>name</t>
   </si>
@@ -44,6 +45,18 @@
     <t>guideline_value</t>
   </si>
   <si>
+    <t>director_gold_coupon</t>
+  </si>
+  <si>
+    <t>director_digital_coupon</t>
+  </si>
+  <si>
+    <t>senior_director_gold_coupon</t>
+  </si>
+  <si>
+    <t>director_tools_coupon</t>
+  </si>
+  <si>
     <t>blocking_amount</t>
   </si>
   <si>
@@ -95,22 +108,94 @@
     <t>Main Branch</t>
   </si>
   <si>
+    <t>Green Valley-2</t>
+  </si>
+  <si>
+    <t>Trichy</t>
+  </si>
+  <si>
+    <t>dtcp_only</t>
+  </si>
+  <si>
+    <t>luxury</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Green Valley-3</t>
+  </si>
+  <si>
+    <t>on_hold</t>
+  </si>
+  <si>
+    <t>Green Valley-4</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Field (column)</t>
+  </si>
+  <si>
+    <t>Type exactly</t>
+  </si>
+  <si>
+    <t>Means (form label)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DTCP + RERA</t>
+  </si>
+  <si>
+    <t>DTCP Only</t>
+  </si>
+  <si>
+    <t>Affordable Project</t>
+  </si>
+  <si>
+    <t>Luxury Project</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>On hold</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
     <t>Column</t>
   </si>
   <si>
     <t>Required</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Notes / valid values</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>Text</t>
+  </si>
+  <si>
     <t>Project name (required, must be unique)</t>
   </si>
   <si>
-    <t>District (required), e.g. Chennai, Trichy</t>
+    <t>Dropdown</t>
+  </si>
+  <si>
+    <t>Dropdown — type one of the values from the Dropdown Values sheet</t>
   </si>
   <si>
     <t>City (required)</t>
@@ -125,19 +210,31 @@
     <t>Extent / area (required), free text</t>
   </si>
   <si>
-    <t>dtcp_rera OR dtcp_only</t>
-  </si>
-  <si>
-    <t>affordable OR luxury</t>
-  </si>
-  <si>
-    <t>draft | active | on_hold | closed (default draft)</t>
+    <t>Dropdown — type exactly: dtcp_rera or dtcp_only</t>
+  </si>
+  <si>
+    <t>Dropdown — type exactly: affordable or luxury</t>
+  </si>
+  <si>
+    <t>Dropdown — type exactly: draft, active, on_hold or closed (default draft)</t>
   </si>
   <si>
     <t>Branch / office (optional)</t>
   </si>
   <si>
     <t>₹ per sq.ft guideline value (optional)</t>
+  </si>
+  <si>
+    <t>Director Gold Coupon ₹ per sq.ft (optional, default 0)</t>
+  </si>
+  <si>
+    <t>Director Digital Coupon ₹ per sq.ft (optional, default 0)</t>
+  </si>
+  <si>
+    <t>Senior Director Gold Coupon ₹ per sq.ft (optional, default 0)</t>
+  </si>
+  <si>
+    <t>Director Tools Coupon ₹ per sq.ft (optional, default 0)</t>
   </si>
   <si>
     <t>Initial block amount ₹ (default 10000)</t>
@@ -183,12 +280,17 @@
       <b/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF3F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -203,9 +305,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,139 +648,381 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="14" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="27" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="24" customWidth="1"/>
-    <col min="15" max="15" width="25" customWidth="1"/>
-    <col min="16" max="16" width="29" customWidth="1"/>
-    <col min="17" max="17" width="25" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="29" customWidth="1"/>
+    <col min="13" max="13" width="33" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="16" max="16" width="27" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="25" customWidth="1"/>
+    <col min="20" max="20" width="29" customWidth="1"/>
+    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="22" max="22" width="28" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>1500</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>10000</v>
       </c>
-      <c r="L2">
+      <c r="P2">
         <v>48</v>
       </c>
-      <c r="M2">
+      <c r="Q2">
         <v>5</v>
       </c>
-      <c r="N2">
+      <c r="R2">
         <v>50000</v>
       </c>
-      <c r="O2">
+      <c r="S2">
         <v>15</v>
       </c>
-      <c r="P2">
+      <c r="T2">
         <v>3</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>5000</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <v>5</v>
       </c>
-      <c r="S2">
+      <c r="W2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>1500</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>10000</v>
+      </c>
+      <c r="P3">
+        <v>48</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>50000</v>
+      </c>
+      <c r="S3">
+        <v>15</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>5000</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>1500</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>10000</v>
+      </c>
+      <c r="P4">
+        <v>48</v>
+      </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
+      <c r="R4">
+        <v>50000</v>
+      </c>
+      <c r="S4">
+        <v>15</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>5000</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>1500</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>10000</v>
+      </c>
+      <c r="P5">
+        <v>48</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>50000</v>
+      </c>
+      <c r="S5">
+        <v>15</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>5000</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
         <v>5000</v>
       </c>
     </row>
@@ -689,89 +1034,67 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -779,142 +1102,418 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="74" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
